--- a/Assets/Data/GameData.xlsx
+++ b/Assets/Data/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\Unity\Projects\ProjectEmergence\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8D865C-584D-4AB9-A3FE-F4934CE7546B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78C8E53-AA03-4BA2-B187-4865BB21C195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="5390" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="5390" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="entities" sheetId="1" r:id="rId1"/>
@@ -1021,16 +1021,10 @@
     <t>它早就已经关上了。</t>
   </si>
   <si>
-    <t>talk_owl</t>
-  </si>
-  <si>
     <t>猫头鹰看着我，用爪子指了指密码箱，呜呜地叫起来。我想我是不精通动物语言的，可我确实地听明白了它想传达的意思：'昼夜轮转的圆脸，沉默地数着一切。等最后一缕呼吸落下，它便会吐出四个数来。'</t>
   </si>
   <si>
     <t>它没有理我。</t>
-  </si>
-  <si>
-    <t>sit_sofa</t>
   </si>
   <si>
     <t>美妙的沙发，美妙的柔软……消磨时光是危险的行为，我不得不起身离开。</t>
@@ -1336,6 +1330,14 @@
   </si>
   <si>
     <t>["一面镜子。镜框上的水垢，坑坑洼洼，起起伏伏，灰白的沉积物上还残留着一层薄薄的冰。盯着它看了太长时间，镜子中的脸好像也有些坑坑洼洼。\n索尼娅惊恐地张着嘴往后退，她靠住墙面。\n镜子里那张挤满鲜嫩肉芽的脸慢了半拍，也腾地一下向后靠去。","被打碎的镜子。我能看见它——\n它和我长着同一张脸，只是那张脸上长满了鲜嫩的肉芽。我想逃，可我的脚、我的腿、我的半边身子，都不再听我的话。\n我的肉体不断增生，亦如我无法挽回的命运与灵魂。"]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>talk_to_owl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sit_on_sofa</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2213,7 +2215,7 @@
         <v>65</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>80</v>
@@ -2677,7 +2679,7 @@
         <v>148</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>149</v>
@@ -3580,22 +3582,22 @@
         <v>298</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>299</v>
@@ -3613,10 +3615,10 @@
         <v>303</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -3627,16 +3629,16 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>9</v>
@@ -3663,7 +3665,7 @@
         <v>9</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="72" x14ac:dyDescent="0.25">
@@ -3677,13 +3679,13 @@
         <v>306</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>307</v>
@@ -3710,7 +3712,7 @@
         <v>314</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="42" x14ac:dyDescent="0.25">
@@ -3721,13 +3723,13 @@
         <v>5</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -3756,13 +3758,13 @@
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -3791,13 +3793,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -3826,13 +3828,13 @@
         <v>4</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -3861,10 +3863,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -3872,14 +3874,14 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -3901,11 +3903,11 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
-        <v>330</v>
+      <c r="K9" s="8" t="s">
+        <v>410</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>27</v>
@@ -3923,7 +3925,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="2"/>
@@ -3935,16 +3937,16 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="O10" s="2"/>
     </row>
@@ -3956,26 +3958,26 @@
         <v>15</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>27</v>
@@ -3995,7 +3997,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="8" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F12" s="2">
         <v>33</v>
@@ -4005,16 +4007,16 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="O12" s="2"/>
     </row>
@@ -4026,19 +4028,19 @@
         <v>25</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F13" s="2">
         <v>20</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -4046,16 +4048,16 @@
         <v>179</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="O13" s="2"/>
     </row>
@@ -4067,7 +4069,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="2"/>
@@ -4079,13 +4081,13 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="M14" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>27</v>
@@ -4100,7 +4102,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="2"/>
@@ -4112,16 +4114,16 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>349</v>
       </c>
       <c r="O15" s="2"/>
     </row>
@@ -4133,13 +4135,13 @@
         <v>17</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -4147,13 +4149,13 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>27</v>
@@ -4173,22 +4175,22 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="238" x14ac:dyDescent="0.25">
@@ -4199,13 +4201,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F18" s="2">
         <v>38</v>
@@ -4217,16 +4219,16 @@
         <v>179</v>
       </c>
       <c r="K18" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="O18" s="2"/>
     </row>
@@ -4238,13 +4240,13 @@
         <v>14</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F19" s="2">
         <v>40</v>
@@ -4254,16 +4256,16 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="O19" s="2"/>
     </row>
@@ -4275,13 +4277,13 @@
         <v>0</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F20" s="2">
         <v>34</v>
@@ -4289,20 +4291,20 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="O20" s="2"/>
     </row>
@@ -4314,13 +4316,13 @@
         <v>19</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F21" s="2">
         <v>34</v>
@@ -4328,20 +4330,20 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="O21" s="2"/>
     </row>
@@ -4353,13 +4355,13 @@
         <v>0</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F22" s="2">
         <v>36</v>
@@ -4369,16 +4371,16 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="M22" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="O22" s="2"/>
     </row>
@@ -4390,13 +4392,13 @@
         <v>19</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F23" s="2">
         <v>36</v>
@@ -4406,16 +4408,16 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="M23" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="O23" s="2"/>
     </row>
@@ -4427,13 +4429,13 @@
         <v>24</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F24" s="2">
         <v>23</v>
@@ -4441,20 +4443,20 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="O24" s="2"/>
     </row>
@@ -4466,13 +4468,13 @@
         <v>21</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F25" s="2">
         <v>23</v>
@@ -4484,22 +4486,22 @@
         <v>27</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="O25" s="2"/>
     </row>
